--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Меры при останове</t>
+          <t>Обстоятельства, при которых произошел останов</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Обстоятельства, при которых произошел останов</t>
+          <t>Меры при останове</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -3278,18 +3278,14 @@
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>При переключении с ГПА№2 на ГПА№3 нагрузка ГПЭС№1 достигла 841 кВт, скачок частоты с 50 до 57,2 Гц вызвал срабатывание защиты и отключение автомата ABB 2500A. ГПЭС№1 остался без нагрузки, АДЭС не запустился, из-за отсутствия питания электродвигателей КВОУ произошел останов ГПА№2 по низкому давлению датчика PDIT 563 A/B.</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>Запуск резервной ГПЭС №3, синхронизация с ГПЭС №1.</t>
-        </is>
-      </c>
+          <t>При переключении с ГПА№2 на ГПА№3 нагрузка ГПЭС№1 достигла 841 кВт, скачок частоты с 50 до 57,2 Гц вызвал срабатывание защиты и отключение автомата ABB 2500A. ГПЭС№1 остался без нагрузки, АДЭС не запустился, из-за отсутствия питания электродвигателей КВОУ произошел останов ГПА№2 по низкому давлению датчика PDIT 563 A/B. Запущена резервная ГПЭС№3, синхронизирована с ГПЭС№1.</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr"/>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>ГПЭС №1 выведен в «резерв».
-Запуск резервной ГПЭС №3, синхронизация с ГПЭС №1.</t>
+          <t xml:space="preserve">ГПЭС №1 выведен в «резерв».
+</t>
         </is>
       </c>
     </row>
@@ -3326,18 +3322,18 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>При повышении оборотов ГТУ №2,3 с 4950 до 5250 об/мин, при переходе режима «АВ»→«АВС» открытие клапана FCV-107 на 19,3% и CDP-клапана FCV-211 на 6,29% снизило давление воздуха в камере сгорания ниже нормы, коэффициент «blowout» превысил предел 15%, произошла потеря пламени.</t>
+          <t>При повышении оборотов ГТУ №2,3 с 4950 до 5250 об/мин, при переходе режима «АВ»→«АВС» открытие клапана FCV-107 на 19,3% и CDP-клапана FCV-211 на 6,29% снизило давление воздуха в камере сгорания ниже нормы, коэффициент «blowout» превысил предел 15%, произошла потеря пламени. Запущен резервный ГПА№1.</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>Запуск резервного ГПА№1. Проверка клапанов CDP/FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
+          <t>Проверка клапанов CDP/FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
           <t>ГПА №3 выведен в «резерв» с исключением режима работы камеры сгорания «АВС». Человеческий фактор персонала исключен.
-Запуск резервного ГПА№1. Проверка клапанов CDP/FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
+Проверка клапанов CDP/FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
         </is>
       </c>
     </row>
@@ -3374,18 +3370,18 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>Зафиксирован Alarm «Flame out trip» — потеря пламени в камере сгорания. Установлено несоответствие значений Т3 в таблицах DLE Mapping зимнего режима значениям, установленным в ПЛК T10, из-за чего при высоких оборотах некорректно работал режим «АВС».</t>
+          <t>Зафиксирован Alarm «Flame out trip» — потеря пламени в камере сгорания. Установлено несоответствие значений Т3 в таблицах DLE Mapping зимнего режима значениям, установленным в ПЛК T10, из-за чего при высоких оборотах некорректно работал режим «АВС». Запущен резервный ГПА№2.</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Запуск резервного ГПА №2. Проверка CDP-клапана FCV-211 и дозирующих клапанов FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
+          <t>Проверка CDP-клапана FCV-211 и дозирующих клапанов FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Человеческий фактор обслуживающего персонала КС-1 исключен.
-Запуск резервного ГПА №2. Проверка CDP-клапана FCV-211 и дозирующих клапанов FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
+Проверка CDP-клапана FCV-211 и дозирующих клапанов FCV-104/105/107, протяжка контактов клапанов и датчиков пламени BE-473 A/B.</t>
         </is>
       </c>
     </row>
@@ -3422,18 +3418,14 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>При активации автоматического режима АСПТ (пожаротушение CO2) сменный инженер вместо кнопки «выбор» нажал «стрелка вправо» и по ошибке активировал команду «пуск АСПТ», введя 4-значный код, что привело к Авто останову ГПА№2 (срабатывание ESDII по алярму CO2 Pre-Discharge).</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>Запуск резервного ГПА №3, ввод в режим МГ за 28 минут.</t>
-        </is>
-      </c>
+          <t>При активации автоматического режима АСПТ (пожаротушение CO2) сменный инженер вместо кнопки «выбор» нажал «стрелка вправо» и по ошибке активировал команду «пуск АСПТ», введя 4-значный код, что привело к Авто останову ГПА№2 (срабатывание ESDII по алярму CO2 Pre-Discharge). Запущен резервный ГПА№3, режим МГ восстановлен за 28 минут.</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr"/>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>ГПА №2 выведен в «резерв». Систему пожаротушения CO2 необходимо модернизировать.
-Запуск резервного ГПА №3, ввод в режим МГ за 28 минут.</t>
+          <t xml:space="preserve">ГПА №2 выведен в «резерв». Систему пожаротушения CO2 необходимо модернизировать.
+</t>
         </is>
       </c>
     </row>
@@ -3518,18 +3510,14 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Из-за отсутствия нагрузочного модуля при запуске вентиляторов АВО газа резко возросла нагрузка и упала частота (382→582 кВт, 49→45 Гц), что вызвало АО ГПЭС№3. Сработала аварийная защита по перепаду давления в баке минерального масла, что привело к автооостанову ГПА №3 и №2.</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>Запуск резервного ГПЭС №1 и ГПА №2,3.</t>
-        </is>
-      </c>
+          <t>Из-за отсутствия нагрузочного модуля при запуске вентиляторов АВО газа резко возросла нагрузка и упала частота (382→582 кВт, 49→45 Гц), что вызвало АО ГПЭС№3. Сработала аварийная защита по перепаду давления в баке минерального масла, что привело к автооостанову ГПА №3 и №2. Запущены резервные ГПЭС№1 и ГПА№2,3.</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>ГПЭС №3 выведен в «резерв», ожидается приезд специалистов ТОО «ГазСервСтрой».
-Запуск резервного ГПЭС №1 и ГПА №2,3.</t>
+          <t xml:space="preserve">ГПЭС №3 выведен в «резерв», ожидается приезд специалистов ТОО «ГазСервСтрой».
+</t>
         </is>
       </c>
     </row>
@@ -3711,18 +3699,18 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Резкое падение давления на выходе воздушного компрессора из-за непрерывного сброса воздуха через открытый клапан XV-3703B осушительной установки ВК№1 (застывшее состояние управляющего ПЛК), а также из-за отсутствия обратного клапана на линии «Воздушный компрессор — Воздушный ресивер».</t>
+          <t>Резкое падение давления на выходе воздушного компрессора из-за непрерывного сброса воздуха через открытый клапан XV-3703B осушительной установки ВК№1 (застывшее состояние управляющего ПЛК), а также из-за отсутствия обратного клапана на линии «Воздушный компрессор — Воздушный ресивер». Выполнено переключение с ВК№1 на ВК№2.</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Переключение ВК с №1 на №2. Перезагрузка ПЛК и комплексное опробование осушительной установки.</t>
+          <t>Перезагрузка ПЛК и комплексное опробование осушительной установки.</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
           <t>ГПА №1,3 перезапущены в работу.
-Переключение ВК с №1 на №2. Перезагрузка ПЛК и комплексное опробование осушительной установки.</t>
+Перезагрузка ПЛК и комплексное опробование осушительной установки.</t>
         </is>
       </c>
     </row>
@@ -3759,18 +3747,18 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Зафиксированы сообщения о срабатывании 2 из 3 датчиков загазованности AE 557 A,B,C. Утечки газа не обнаружено. Причина — кратковременная потеря связи (потеря пакета данных) на коммутаторах NTRON 509 системы управления HIMA.</t>
+          <t>Зафиксированы сообщения о срабатывании 2 из 3 датчиков загазованности AE 557 A,B,C. Утечки газа не обнаружено. Причина — кратковременная потеря связи (потеря пакета данных) на коммутаторах NTRON 509 системы управления HIMA. Запущен резервный ГПА№2.</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Запуск резервного ГПА №2. Замена коммутаторов NTRON 509 системы HIMA. Калибровка датчиков загазованности AE 557 A,B,C.</t>
+          <t>Замена коммутаторов NTRON 509 системы HIMA. Калибровка датчиков загазованности AE 557 A,B,C.</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
           <t>Человеческий фактор персонала КС-1 исключен.
-Запуск резервного ГПА №2. Замена коммутаторов NTRON 509 системы HIMA. Калибровка датчиков загазованности AE 557 A,B,C.</t>
+Замена коммутаторов NTRON 509 системы HIMA. Калибровка датчиков загазованности AE 557 A,B,C.</t>
         </is>
       </c>
     </row>
@@ -3807,18 +3795,18 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Обнаружены нестабильные обороты ГПЭС№1; при запуске ГПЭС№3 и №2 синхронизация с ГПЭС№1 не была произведена. Колебания оборотов вызвали колебания частоты сети (45–52 Гц), сработала защита по частоте, ГПЭС№1 остался без нагрузки — произошел останов ГПА№1.</t>
+          <t>Обнаружены нестабильные обороты ГПЭС№1; при запуске ГПЭС№3 и №2 синхронизация с ГПЭС№1 не была произведена. Колебания оборотов вызвали колебания частоты сети (45–52 Гц), сработала защита по частоте, ГПЭС№1 остался без нагрузки — произошел останов ГПА№1. Запущены резервные ГПЭС№2,3, выполнена синхронизация.</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Запуск резервных ГПЭС №2, №3 и синхронизация. Проверка трендов, бороскопия цилиндров, ревизия генераторов, турбокомпрессоров — дефектов не обнаружено. Замена 16 свечей зажигания.</t>
+          <t>Проверка трендов, бороскопия цилиндров, ревизия генераторов, турбокомпрессоров — дефектов не обнаружено. Замена 16 свечей зажигания.</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
           <t>ГПЭС №1 выведен в «резерв».
-Запуск резервных ГПЭС №2, №3 и синхронизация. Проверка трендов, бороскопия цилиндров, ревизия генераторов, турбокомпрессоров — дефектов не обнаружено. Замена 16 свечей зажигания.</t>
+Проверка трендов, бороскопия цилиндров, ревизия генераторов, турбокомпрессоров — дефектов не обнаружено. Замена 16 свечей зажигания.</t>
         </is>
       </c>
     </row>
@@ -3903,19 +3891,19 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Сильный посторонний шум и резкое снижение частоты ГПЭС№3 (49→43 Гц) привели к вынужденному останову ГПЭС№3. Из-за кратковременного обесточивания вспомогательных систем сработала защита по перепаду давления PDIT-563 в кожухе ГПА №1,3, что вызвало АвтО ГПА №1 и №3.</t>
+          <t>Сильный посторонний шум и резкое снижение частоты ГПЭС№3 (49→43 Гц) привели к вынужденному останову ГПЭС№3. Из-за кратковременного обесточивания вспомогательных систем сработала защита по перепаду давления PDIT-563 в кожухе ГПА №1,3, что вызвало АвтО ГПА №1 и №3. Запущена резервная ГПЭС№2, ГПА№1,3 возвращены в работу.</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>Запуск резервной ГПЭС №2 и ГПА №1,3.
+          <t xml:space="preserve">
 Повреждено: Выявлены дефекты (повреждение) выпускных клапанов в цилиндрах №2,4,6,8,9,11 ГПЭС№3</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>ГПЭС №3 выведен в «ремонт» — требуется замена ГБЦ №2,4,6,8,9,11.
-Запуск резервной ГПЭС №2 и ГПА №1,3.</t>
+          <t xml:space="preserve">ГПЭС №3 выведен в «ремонт» — требуется замена ГБЦ №2,4,6,8,9,11.
+</t>
         </is>
       </c>
     </row>
@@ -4001,18 +3989,18 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>Некорректная работа позиционера клапана XV 222 — потеря сигнала обратной связи от позиционера о закрытии клапана, что привело к автоматическому останову ГПА№1.</t>
+          <t>Некорректная работа позиционера клапана XV 222 — потеря сигнала обратной связи от позиционера о закрытии клапана, что привело к автоматическому останову ГПА№1. Пуск резервного ГПА№3, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>Заменён позиционер клапана XV 222; выполнен ремонт концевых магнитных датчиков (установлены дополнительные металлические пластины для усиления магнитного эффекта). Выполнен автоматический пуск с восстановлением режима работы МГ.</t>
+          <t>Заменён позиционер клапана XV 222; выполнен ремонт концевых магнитных датчиков (установлены дополнительные металлические пластины для усиления магнитного эффекта).</t>
         </is>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
           <t>ГПА №1 выведен в «резерв».
-Заменён позиционер клапана XV 222; выполнен ремонт концевых магнитных датчиков (установлены дополнительные металлические пластины для усиления магнитного эффекта). Выполнен автоматический пуск с восстановлением режима работы МГ.</t>
+Заменён позиционер клапана XV 222; выполнен ремонт концевых магнитных датчиков (установлены дополнительные металлические пластины для усиления магнитного эффекта).</t>
         </is>
       </c>
     </row>
@@ -4049,18 +4037,18 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Самопроизвольное отключение вводного автомата шкафа управления АВО антифриза привело к останову всех вентиляторов охлаждения. В результате температура антифриза выросла с 94°C до 106°C, что вызвало автоматический останов ГПА№1, затем ГПА№2.</t>
+          <t>Самопроизвольное отключение вводного автомата шкафа управления АВО антифриза привело к останову всех вентиляторов охлаждения. В результате температура антифриза выросла с 94°C до 106°C, что вызвало автоматический останов ГПА№1, затем ГПА№2. Пуск резервного ГПЭС№2, пуск ГПА№2,3, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Произведена замена вводного автомата шкафа управления АВО антифриза на ГПА№1. Выполнен пуск резервного ГПА, восстановлен режим работы МГ.</t>
+          <t>Произведена замена вводного автомата шкафа управления АВО антифриза на ГПА№1.</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
           <t>ГПА №1 выведен в «резерв».
-Произведена замена вводного автомата шкафа управления АВО антифриза на ГПА№1. Выполнен пуск резервного ГПА, восстановлен режим работы МГ.</t>
+Произведена замена вводного автомата шкафа управления АВО антифриза на ГПА№1.</t>
         </is>
       </c>
     </row>
@@ -4097,18 +4085,18 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Некорректное отображение обратной связи о рабочем положении клапана FCV-780 (Hot bypass), что привело к вынужденному нормальному останову ГПА№3.</t>
+          <t>Некорректное отображение обратной связи о рабочем положении клапана FCV-780 (Hot bypass), что привело к вынужденному нормальному останову ГПА№3. Пуск резервного ГПА№2, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>Произведена протяжка креплений механизма концевого выключателя датчика рабочего положения клапана FCV-780 (Hot bypass). Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+          <t>Произведена протяжка креплений и механизма концевого выключателя датчика рабочего положения клапана FCV-780 (Hot bypass).</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
           <t>ГПА №3 выведен в «резерв».
-Произведена протяжка креплений механизма концевого выключателя датчика рабочего положения клапана FCV-780 (Hot bypass). Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+Произведена протяжка креплений и механизма концевого выключателя датчика рабочего положения клапана FCV-780 (Hot bypass).</t>
         </is>
       </c>
     </row>
@@ -4145,18 +4133,18 @@
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Отказ датчика температуры (со стороны активного подпятника) TE 403-1, что привело к вынужденному нормальному останову ГПА№2.</t>
+          <t>Отказ датчика температуры (со стороны активного подпятника) TE 403-1, что привело к вынужденному нормальному останову ГПА№2. Пуск резервного ГПА№1, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 403-1A и TE 403-1B в клеммной коробке ТВ3, подключён резервный датчик TE 403-1B, протянуты контактные группы в клеммной коробке. Выполнен пуск резервного ГПА, восстановлен режим работы МГ.</t>
+          <t>Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 403-1A и TE 403-1B в клеммной коробке ТВ3, подключён резервный датчик TE 403-1B, протянуты контактные группы в клеммной коробке.</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
           <t>ГПА №2 выведен в «резерв».
-Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 403-1A и TE 403-1B в клеммной коробке ТВ3, подключён резервный датчик TE 403-1B, протянуты контактные группы в клеммной коробке. Выполнен пуск резервного ГПА, восстановлен режим работы МГ.</t>
+Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 403-1A и TE 403-1B в клеммной коробке ТВ3, подключён резервный датчик TE 403-1B, протянуты контактные группы в клеммной коробке.</t>
         </is>
       </c>
     </row>
@@ -4193,18 +4181,18 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Отказ датчика температуры (со стороны активного подпятника) TE 401-1, что привело к вынужденному нормальному останову ГПА№2.</t>
+          <t>Отказ датчика температуры (со стороны активного подпятника) TE 401-1, что привело к вынужденному нормальному останову ГПА№2. Пуск резервного ГПА№1, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 401-1A и TE 401-1B в клеммной коробке ТВ3, подключён резервный датчик TE 401-1B, протянуты контактные группы в клеммной коробке. Выполнен пуск резервного ГПА№1, восстановлен режим работы МГ.</t>
+          <t>Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 401-1A и TE 401-1B в клеммной коробке ТВ3, подключён резервный датчик TE 401-1B, протянуты контактные группы в клеммной коробке.</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
           <t>ГПА №2 выведен в «резерв».
-Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 401-1A и TE 401-1B в клеммной коробке ТВ3, подключён резервный датчик TE 401-1B, протянуты контактные группы в клеммной коробке. Выполнен пуск резервного ГПА№1, восстановлен режим работы МГ.</t>
+Выполнена ревизия проводов и соединений, проверена целостность цепей датчиков температуры TE 401-1A и TE 401-1B в клеммной коробке ТВ3, подключён резервный датчик TE 401-1B, протянуты контактные группы в клеммной коробке.</t>
         </is>
       </c>
     </row>
@@ -4241,18 +4229,18 @@
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Отказ датчика температуры охлаждающей жидкости ГПЭС№3 привёл к автоматическому останову ГПЭС№3 и последующему автоматическому останову ГПА№1,3.</t>
+          <t>Отказ датчика температуры охлаждающей жидкости ГПЭС№3 привёл к автоматическому останову ГПЭС№3 и последующему автоматическому останову ГПА№1,3. Пуск резервного ГПЭС№1, пуск ГПА№1,3, режим работы МГ восстановлен.</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Произведена замена датчика температуры охлаждающей жидкости на ГПЭС№3. Выполнен пуск резервного ГПЭС№1, пуск ГПА№1,3, восстановлен режим работы МГ.</t>
+          <t>Произведена замена датчика температуры охлаждающей жидкости на ГПЭС№3.</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
           <t>ГПЭС №3 выведен в «резерв».
-Произведена замена датчика температуры охлаждающей жидкости на ГПЭС№3. Выполнен пуск резервного ГПЭС№1, пуск ГПА№1,3, восстановлен режим работы МГ.</t>
+Произведена замена датчика температуры охлаждающей жидкости на ГПЭС№3.</t>
         </is>
       </c>
     </row>
@@ -4289,18 +4277,18 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Высокие показания датчика вибрации газогенератора VT-457 (225 мм/с) при выходе ГПА№1 в режим холостого хода (обороты ГГ 6800 об/мин) привели к вынужденному нормальному останову.</t>
+          <t>Высокие показания датчика вибрации газогенератора VT-457 (225 мм/с) при выходе ГПА№1 в режим холостого хода (обороты ГГ 6800 об/мин) привели к вынужденному нормальному останову. Пуск резервного ГПА№2, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>Выполнена ревизия проводов и соединений, проверка и прозвонка датчика вибрации VT-457 и датчиков стружки синтетического масла. Проведена бороскопическая инспекция газогенератора ГПА№1 согласно рекомендациям GE. Выполнен пробный пуск ГПА№1 в режиме холостого хода (обороты ГГ 6800 об/мин) на 5 минут — отклонений в параметрах ГГ не обнаружено. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+          <t>Выполнена ревизия проводов и соединений, проверка и прозвонка датчика вибрации VT-457 и датчиков стружки синтетического масла. Проведена бороскопическая инспекция газогенератора ГПА№1 согласно рекомендациям GE. Выполнен пробный пуск ГПА№1 в режиме холостого хода (обороты ГГ 6800 об/мин) на 5 минут — отклонений в параметрах ГГ не обнаружено.</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
           <t>ГПА №1 выведен в «резерв».
-Выполнена ревизия проводов и соединений, проверка и прозвонка датчика вибрации VT-457 и датчиков стружки синтетического масла. Проведена бороскопическая инспекция газогенератора ГПА№1 согласно рекомендациям GE. Выполнен пробный пуск ГПА№1 в режиме холостого хода (обороты ГГ 6800 об/мин) на 5 минут — отклонений в параметрах ГГ не обнаружено. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+Выполнена ревизия проводов и соединений, проверка и прозвонка датчика вибрации VT-457 и датчиков стружки синтетического масла. Проведена бороскопическая инспекция газогенератора ГПА№1 согласно рекомендациям GE. Выполнен пробный пуск ГПА№1 в режиме холостого хода (обороты ГГ 6800 об/мин) на 5 минут — отклонений в параметрах ГГ не обнаружено.</t>
         </is>
       </c>
     </row>
@@ -4337,18 +4325,18 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Отказ микропроцессора вводного автомата К51-PR122/P ГПЭС№3, что привело к автоматическому останову ГПЭС№3 и последующему автоматическому останову ГПА№1,3.</t>
+          <t>Отказ микропроцессора вводного автомата К51-PR122/P ГПЭС№3, что привело к автоматическому останову ГПЭС№3 и последующему автоматическому останову ГПА№1,3. Пуск резервного ГПЭС№1,2, пуск ГПА№1,2, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Произведена замена микропроцессора вводного автомата К51-PR122/P ГПЭС№3. Выполнен пуск резервного ГПЭС№1,2, пуск ГПА№1,2, восстановлен режим работы МГ.</t>
+          <t>Произведена замена микропроцессора вводного автомата К51-PR122/P ГПЭС№3.</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
           <t>ГПЭС №3 выведен в «резерв».
-Произведена замена микропроцессора вводного автомата К51-PR122/P ГПЭС№3. Выполнен пуск резервного ГПЭС№1,2, пуск ГПА№1,2, восстановлен режим работы МГ.</t>
+Произведена замена микропроцессора вводного автомата К51-PR122/P ГПЭС№3.</t>
         </is>
       </c>
     </row>
@@ -4385,18 +4373,18 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Ослабление контакта предохранителя CDVR ГПЭС№1 привело к автоматическому останову ГПЭС№1 и последующему автоматическому останову ГПА№1,2.</t>
+          <t>Ослабление контакта предохранителя CDVR ГПЭС№1 привело к автоматическому останову ГПЭС№1 и последующему автоматическому останову ГПА№1,2. Пуск резервного ГПЭС№2,3, пуск ГПА№1,3, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Произведена замена предохранительной колодки ГПЭС№1. Выполнен пуск резервного ГПЭС№2,3, пуск ГПА№1,3, восстановлен режим работы МГ.</t>
+          <t>Произведена замена предохранительной колодки ГПЭС№1.</t>
         </is>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
           <t>ГПЭС №1 выведен в «резерв».
-Произведена замена предохранительной колодки ГПЭС№1. Выполнен пуск резервного ГПЭС№2,3, пуск ГПА№1,3, восстановлен режим работы МГ.</t>
+Произведена замена предохранительной колодки ГПЭС№1.</t>
         </is>
       </c>
     </row>
@@ -4433,19 +4421,19 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Кратковременная потеря показаний рабочих параметров ГПА№3, поступающих от модуля ввода/вывода MTL8000 UCP-1, что привело к срабатыванию защиты и переводу ГПА№3 в безопасный режим холостого хода (6800 об/мин).</t>
+          <t>Кратковременная потеря показаний рабочих параметров ГПА№3, поступающих от модуля ввода/вывода MTL8000 UCP-1, что привело к срабатыванию защиты и переводу ГПА№3 в безопасный режим холостого хода (6800 об/мин). Пуск резервного ГПА№2, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Выполнена переборка узла крепления несущих плат блока модулей ввода/вывода MTL8000 UCP-1 ГПА№3. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.
+          <t>Выполнена переборка узла крепления несущих плат блока модулей ввода/вывода MTL8000 UCP-1 ГПА№3.
 Повреждено: Отсутствует</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
           <t>ГПА №3 выведен в «резерв».
-Выполнена переборка узла крепления несущих плат блока модулей ввода/вывода MTL8000 UCP-1 ГПА№3. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+Выполнена переборка узла крепления несущих плат блока модулей ввода/вывода MTL8000 UCP-1 ГПА№3.</t>
         </is>
       </c>
     </row>
@@ -4531,19 +4519,19 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>При переключении ГПЭС с №2 на №3 ведущий инженер ЭВС и ЭХЗ ошибочно перевёл тумблер панели рабочего ГПЭС№2 (находившегося в режиме «Ручной») в режим «Авто», что привело к сбросу нагрузки с ГПЭС№2. При повторной синхронизации нагрузка не была полностью передана на ГПЭС№2, что привело к автоматическому останову ГПА№1,2.</t>
+          <t>При переключении ГПЭС с №2 на №3 ведущий инженер ЭВС и ЭХЗ ошибочно перевёл тумблер панели рабочего ГПЭС№2 (находившегося в режиме «Ручной») в режим «Авто», что привело к сбросу нагрузки с ГПЭС№2. При повторной синхронизации нагрузка не была полностью передана на ГПЭС№2, что привело к автоматическому останову ГПА№1,2. Дана нагрузка на ГПЭС№2, восстановлена цепь электропитания на МСС. Выполнен пуск ГПА№3, затем ГПА№1.</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Дана нагрузка на ГПЭС№2, замкнута цепь электропитания на МСС. Выполнен пуск ГПА№3, затем ГПА№1.
+          <t xml:space="preserve">
 Повреждено: Не обнаружено</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>ГПЭС №2 выведен в режим работы, АДЭС выведен в резерв. ГПА №1 в работе, ГПА №2 в резерве.
-Дана нагрузка на ГПЭС№2, замкнута цепь электропитания на МСС. Выполнен пуск ГПА№3, затем ГПА№1.</t>
+          <t xml:space="preserve">ГПЭС №2 выведен в режим работы, АДЭС выведен в резерв. ГПА №1 в работе, ГПА №2 в резерве.
+</t>
         </is>
       </c>
     </row>
@@ -4580,18 +4568,18 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Потеря связи между Mark VIe и контроллером системы пожаротушения HIMatrix F35 01030 вызвала сигнал «HIMA FIRE FIGHTING CPUA UCP2 – HEARTBEAT FAILURE ALARM», что привело к автоматическому останову ГПА№3 со стравливанием контура.</t>
+          <t>Потеря связи между Mark VIe и контроллером системы пожаротушения HIMatrix F35 01030 вызвала сигнал «HIMA FIRE FIGHTING CPUA UCP2 – HEARTBEAT FAILURE ALARM», что привело к автоматическому останову ГПА№3 со стравливанием контура. Пуск резервного ГПА№2, восстановление режима работы МГ.</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Изменены параметры программного обеспечения в контроллерах безопасности Safety CPU A/B и пожаротушения FF CPU A/B системы HIMatrix, устранена неполадка резервирования центральных процессоров. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+          <t>Изменены параметры программного обеспечения в контроллерах безопасности Safety CPU A/B и пожаротушения FF CPU A/B системы HIMatrix, устранена неполадка резервирования центральных процессоров.</t>
         </is>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
           <t>ГПА №3 выведен в «резерв».
-Изменены параметры программного обеспечения в контроллерах безопасности Safety CPU A/B и пожаротушения FF CPU A/B системы HIMatrix, устранена неполадка резервирования центральных процессоров. Выполнен пуск резервного ГПА№2, восстановлен режим работы МГ.</t>
+Изменены параметры программного обеспечения в контроллерах безопасности Safety CPU A/B и пожаротушения FF CPU A/B системы HIMatrix, устранена неполадка резервирования центральных процессоров.</t>
         </is>
       </c>
     </row>

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -3231,7 +3231,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Причина (описание)</t>
+          <t>Обстоятельства, при которых произошел останов (п.6)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -599,7 +599,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>БАЗА ДАННЫХ ПО АВАРИЙНЫМ ОСТАНОВАМ ГПА</t>
+          <t>БАЗА ДАННЫХ ПО АВТО ОСТАНОВАМ ГПА</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       <c r="I10" s="15" t="inlineStr">
         <is>
           <t>ГПА №2 выведен в «резерв».
-Внедрено резервирование контроля давления в системе сухих газовых уплотнений (СГУ) ГПА GE согласно предложению по повышению эффективности №4 от 28.11.2025. Установлен резервный датчик давления PIT-750/B (Rosemount 3051) параллельно основному датчику PIT-750 с использованием существующей аппаратной базы. Резервный датчик подключён к свободному аналоговому входу №4 модуля MTL8000 8201-HI-IS в шкафу JB-1. Настроена логика контроллера по принципу голосования «2оо2»: останов ГПА инициируется только при подтверждении аварийного значения давления обоими датчиками либо при совпадении аварийного сигнала одного датчика с диагностической неисправностью второго. На ЧМИ (HMI Cimplicity GE) обеспечено отображение параметров обоих каналов измерения, состояния датчиков и диагностической информации. Обеспечено резервирование системы контроля давления СГУ с исключением потери функции контроля при выходе из строя одного измерительного канала. — Акт выполненных работ Акт выполненных работ от 23.05.2026 от 23.05.2026 (выполнено)</t>
+Внедрено резервирование контроля давления в системе сухих газовых уплотнений (СГУ) ГПА GE согласно предложению по повышению эффективности №4 от 28.11.2025. Установлен резервный датчик давления PIT-750/B (Rosemount 3051) параллельно основному датчику PIT-750 с использованием существующей аппаратной базы. Резервный датчик подключён к свободному аналоговому входу №4 модуля MTL8000 8201-HI-IS в шкафу JB-1. Настроена логика контроллера по принципу голосования «2оо2»: останов ГПА инициируется только при подтверждении аварийного значения давления обоими датчиками либо при совпадении аварийного сигнала одного датчика с диагностической неисправностью второго. На ЧМИ (HMI Cimplicity GE) обеспечено отображение параметров обоих каналов измерения, состояния датчиков и диагностической информации. Обеспечено резервирование системы контроля давления СГУ с исключением потери функции контроля при выходе из строя одного измерительного канала. — Акт выполненных работ  от 23.05.2026 (выполнено)</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       <c r="I18" s="15" t="inlineStr">
         <is>
           <t>ГПА №2 выведен в режим «резерв».
-Ревизия CDP клапана (Bleed Valve) S/N GRTR7704: наружный осмотр корпуса и привода; демонтаж привода; демонтаж и инспекция элементов корпуса; инспекция штока и элементов поршневого затвора; обратная сборка всех элементов клапана после ревизии. По результатам ревизии подтверждён износ тефлонового уплотнительного кольца поршневого затвора как причина утечки. — Акт выполненных работ Акт выполненных работ от 04.06.2023 от 04.06.2023 (выполнено)</t>
+Ревизия CDP клапана (Bleed Valve) S/N GRTR7704: наружный осмотр корпуса и привода; демонтаж привода; демонтаж и инспекция элементов корпуса; инспекция штока и элементов поршневого затвора; обратная сборка всех элементов клапана после ревизии. По результатам ревизии подтверждён износ тефлонового уплотнительного кольца поршневого затвора как причина утечки. — Акт выполненных работ  от 04.06.2023 (выполнено)</t>
         </is>
       </c>
     </row>
@@ -4997,11 +4997,7 @@
           <t>Внедрено резервирование контроля давления в системе сухих газовых уплотнений (СГУ) ГПА GE согласно предложению по повышению эффективности №4 от 28.11.2025. Установлен резервный датчик давления PIT-750/B (Rosemount 3051) параллельно основному датчику PIT-750 с использованием существующей аппаратной базы. Резервный датчик подключён к свободному аналоговому входу №4 модуля MTL8000 8201-HI-IS в шкафу JB-1. Настроена логика контроллера по принципу голосования «2оо2»: останов ГПА инициируется только при подтверждении аварийного значения давления обоими датчиками либо при совпадении аварийного сигнала одного датчика с диагностической неисправностью второго. На ЧМИ (HMI Cimplicity GE) обеспечено отображение параметров обоих каналов измерения, состояния датчиков и диагностической информации. Обеспечено резервирование системы контроля давления СГУ с исключением потери функции контроля при выходе из строя одного измерительного канала.</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Акт выполненных работ от 23.05.2026</t>
-        </is>
-      </c>
+      <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="14" t="inlineStr">
         <is>
           <t>23.05.2026</t>
@@ -5037,11 +5033,7 @@
           <t>Ревизия CDP клапана (Bleed Valve) S/N GRTR7704: наружный осмотр корпуса и привода; демонтаж привода; демонтаж и инспекция элементов корпуса; инспекция штока и элементов поршневого затвора; обратная сборка всех элементов клапана после ревизии. По результатам ревизии подтверждён износ тефлонового уплотнительного кольца поршневого затвора как причина утечки.</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Акт выполненных работ от 04.06.2023</t>
-        </is>
-      </c>
+      <c r="F5" s="13" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
           <t>04.06.2023</t>

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1839,8 +1839,372 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>25.04.2025</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2025-№1</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act01_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>02.07.2025</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2025-№2</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act02_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>02.07.2025</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2025-№2</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act02_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>12.07.2025</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2025-№3</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act03_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>24.07.2025</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>2025-№4</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act04_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>24.07.2025</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>2025-№4</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act04_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>03.08.2025</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2025-№5</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act05_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>03.08.2025</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>2025-№5</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act05_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>07.08.2025</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2025-№6</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act06_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>08.08.2025</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2025-№7</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act07_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>14.09.2025</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2025-№8</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act08_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>18.11.2025</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>2025-№10</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act10_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>19.11.2025</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2025-№10</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>kc2_act10_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Этот лист формируется автоматически из accidents.json при запуске build.py. Не редактируйте его вручную — правки потеряются при следующей пересборке.</t>
         </is>
@@ -1848,8 +2212,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1861,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2905,6 +3269,336 @@
       </c>
       <c r="G33" s="7" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№1 из-за потери связи контроллера ECS с MOOG DS2000XP</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>25.04.2025</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Останов ГПА№1,3 из-за автоматического останова ГПЭС№1 (детонация цилиндра №2)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>02.07.2025</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №3</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№1 по сигналу Central Metering Valve Failure Shutdown (модернизированный контроллер HC-DRIVER)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>12.07.2025</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>№3</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Останов ГПА№2,3 из-за автоматического останова ГПЭС№3 (неисправность модуля управления электроникой CAT 348-2392)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>24.07.2025</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>№4</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2, ГПА №3</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Останов ГПА№1,3 из-за автоматического останова ГПЭС№2 (детонация цилиндра №1)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>03.08.2025</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>№5</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №3</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№1 по сигналу Secondary Metering Valve Failure Shutdown (неисправность контроллера HC-Drive Secondary)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>07.08.2025</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>№6</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№3 из-за активации кнопки ESD-3 сотрудниками подрядной организации на УЗПОУ-2</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>08.08.2025</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>№7</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Вынужденный нормальный останов ГПА№3 из-за превышения температуры газа при переключении с ГПА№1</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>14.09.2025</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>№8</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№1 без стравливания контура из-за потери статуса положения крана MOV-4101 (1-й случай, повторился 19.11.2025)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>18.11.2025</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>№10</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Повторный автоматический останов ГПА№1 без стравливания контура из-за потери статуса положения крана MOV-4101 (2-й случай)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>19.11.2025</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>№10</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2942,6 +3636,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2996,15 +3700,15 @@
         <v>2018</v>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A4,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3013,15 +3717,15 @@
         <v>2019</v>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A5,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3030,15 +3734,15 @@
         <v>2020</v>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A6,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3047,15 +3751,15 @@
         <v>2021</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A7,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3064,15 +3768,15 @@
         <v>2022</v>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A8,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3081,15 +3785,15 @@
         <v>2023</v>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A9,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3098,15 +3802,15 @@
         <v>2024</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A10,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3115,15 +3819,15 @@
         <v>2025</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A11,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3132,15 +3836,15 @@
         <v>2026</v>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$46,База_данных!$A$4:$A$46,A12,База_данных!$B$4:$B$46,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3151,15 +3855,15 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$46,База_данных!$B$4:$B$46,"ГПА №1")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №1")</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$46,База_данных!$B$4:$B$46,"ГПА №2")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №2")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$46,База_данных!$B$4:$B$46,"ГПА №3")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №3")</f>
         <v/>
       </c>
     </row>
@@ -3177,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4680,6 +5384,488 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="95" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>№1 от 25.04.2025</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>25.04.2025</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>При нормальной работе ГПА№1 поступили сигналы автоматического останова «EMV DeviceNet Card Comms Failure Shutdown», «Central Metering Valve Failure Shutdown», «Primary Metering Valve Failure Shutdown», «Secondary Metering Valve Failure Shutdown». Причиной послужила кратковременная потеря связи контроллера ECS с контроллерами MOOG DS2000XP, управляющими топливными клапанами Central, Primary, Secondary.</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Визуальный осмотр панелей управления TLCP, UCP. Перезагрузка контроллеров управления клапанами Moog EMV. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, Moog EMV.</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Визуальный осмотр панелей управления TLCP, UCP. Перезагрузка контроллеров управления клапанами Moog EMV. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, Moog EMV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="95" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>№2 от 02.07.2025</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>02.07.2025</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №3</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Электросеть / переключение агрегатов</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>02.07.2025 в 12:15 произошёл авто останов ГПЭС№1 по сигналу «AL4» «ОБЩАЯ НЕИСПРАВНОСТЬ». В 12:15 включился в работу АДЭС. В 12:20 произведён пуск ГПЭС№2, восстановлено электроснабжение станции КС-2 и ВП. В 12:21 нормальный останов АДЭС. Диагностика Caterpillar Electronic Technician зафиксировала код ошибки E402(3): детонация в цилиндре №2 двигателя ГПЭС№1, что привело к её аварийной остановке и, как следствие, к автоматическому отключению работающих ГПА№1 и №3.</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика ГПЭС№1 (Caterpillar Electronic Technician). Бороскопическая инспекция цилиндра №2 — повреждений и дефектов не обнаружено. Разборка крышки цилиндра, проверка тепловых зазоров клапанов — в пределах нормы. Проверка свечи зажигания цилиндра №2 — обнаружено значительное количество углеродистых отложений и незначительное механическое повреждение (скол).</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Компьютерная диагностика ГПЭС№1 (Caterpillar Electronic Technician). Бороскопическая инспекция цилиндра №2 — повреждений и дефектов не обнаружено. Разборка крышки цилиндра, проверка тепловых зазоров клапанов — в пределах нормы. Проверка свечи зажигания цилиндра №2 — обнаружено значительное количество углеродистых отложений и незначительное механическое повреждение (скол).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="95" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>№3 от 12.07.2025</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>12.07.2025</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>12.07.2025 в 1:32 поступил сигнал автоматического останова «Central Metering Valve Failure Shutdown» EC1_LSS65UC044. На ГПА-1 был произведён монтаж модернизированных контроллеров HC-DRIVER вместо MOOG DS2000XP, в связи с чем возможна некорректная работа логики или механической части заменённого контроллера HC-DRIVER (Central).</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Визуальный осмотр панелей управления TLCP, UCP. Перезагрузка контроллера управления клапаном HC-DRIVER EMV Central. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, HC-DRIVER EMV, клеммных соединений реле безопасности 3FFSE, кабелей клапана Central топливной линии.</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Визуальный осмотр панелей управления TLCP, UCP. Перезагрузка контроллера управления клапаном HC-DRIVER EMV Central. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, HC-DRIVER EMV, клеммных соединений реле безопасности 3FFSE, кабелей клапана Central топливной линии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="95" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>№4 от 24.07.2025</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>24.07.2025</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2, ГПА №3</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>24.07.2025 в 03:04 произошёл авто останов ГПЭС№3 по сигналам «262-3» (источник питания 5В для датчиков показывает напряжение выше нормы), «336-2» (переключатель управления двигателем: хаотичный, прерывистый или неисправный) и «100-2» (датчик давления масла в двигателе: хаотичный, прерывистый или неверный), обнаруженным программой Caterpillar Electronic Technician. Измерение напряжения датчиков давления масла до и после фильтров показало 12 вольт вместо требуемых по схеме генератора Caterpillar G3516C GZC1-UP 5 вольт. На аналогичных датчиках исправной резервной ГПЭС напряжение соответствует норме (5В). Установлено, что модуль управления электроникой двигателя (парт-номер CAT 348-2392) неисправен.</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика ГПЭС№3 (Caterpillar Electronic Technician). Измерение напряжения на датчиках давления масла до и после фильтров. Сравнение показаний с аналогичными датчиками исправной резервной ГПЭС.
+Повреждено: Модуль управления электроникой двигателя CAT 348-2392 — неисправен, требуется замена</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Компьютерная диагностика ГПЭС№3 (Caterpillar Electronic Technician). Измерение напряжения на датчиках давления масла до и после фильтров. Сравнение показаний с аналогичными датчиками исправной резервной ГПЭС.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="95" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>№5 от 03.08.2025</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>03.08.2025</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №3</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Электросеть / переключение агрегатов</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>03.08.2025 в 14:52 произошёл авто останов ГПЭС№2 по сигналу «AL4» «ОБЩАЯ НЕИСПРАВНОСТЬ». В 14:52 включился АДЭС, в 14:55 произведён пуск ГПЭС№1, восстановлено электроснабжение станции КС-2 и ВП, произведён нормальный останов АДЭС. Диагностика Caterpillar Electronic Technician зафиксировала код ошибки E402(3): детонация в цилиндре №1 двигателя ГПЭС№2, что привело к её аварийной остановке и, как следствие, к автоматическому отключению работающих ГПА№1 и №3.</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика ГПЭС№2 (Caterpillar Electronic Technician). Бороскопическая инспекция цилиндра №1 — повреждений и дефектов не обнаружено. Проверка свечи зажигания цилиндра №1 — обнаружено значительное количество углеродистых отложений и незначительное механическое повреждение (скол).</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Компьютерная диагностика ГПЭС№2 (Caterpillar Electronic Technician). Бороскопическая инспекция цилиндра №1 — повреждений и дефектов не обнаружено. Проверка свечи зажигания цилиндра №1 — обнаружено значительное количество углеродистых отложений и незначительное механическое повреждение (скол).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="95" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>№6 от 07.08.2025</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>07.08.2025</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>07.08.2025 в 13:14 поступил сигнал автоматического останова «Secondary Metering Valve Failure Shutdown» EC1_LSS65UC046. На ГПА-1 ранее были установлены модернизированные контроллеры HC-DRIVER вместо MOOG DS2000XP. В ходе выяснения причины выявлен неисправный контроллер HC-Drive (Secondary) S\N 0030.</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Произведена замена модернизированного контроллера HC-Drive на MOOG DS2000XP, который стоял до модернизации, в связи с некорректной работой HC-Drive S\N 0030 (Secondary). Визуальный осмотр панелей TLCP, UCP. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, EMV, клеммных соединений реле безопасности 3FFSE, кабелей клапана Secondary топливной линии.
+Повреждено: Контроллер HC-Drive (Secondary) S\N 0030 — неисправен, заменён на MOOG DS2000XP</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Произведена замена модернизированного контроллера HC-Drive на MOOG DS2000XP, который стоял до модернизации, в связи с некорректной работой HC-Drive S\N 0030 (Secondary). Визуальный осмотр панелей TLCP, UCP. Перезагрузка модуля DeviceNet системы ECS в шкафу UCP. Проверка хода топливных клапанов (в норме). Протяжка контактов TLCP, EMV, клеммных соединений реле безопасности 3FFSE, кабелей клапана Secondary топливной линии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="95" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>№7 от 08.08.2025</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>08.08.2025</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Человеческий фактор</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>08.08.2025 в 14:35 поступил сигнал активации кнопки аварийного останова ESD-3 (тег CS2-29SB1101) в зоне УЗПОУ-2, где в это время проводились работы подрядной организации АО ИЦА (гидроизоляция фундаментов ограждения). Сотрудники АО ИЦА не сообщили диспетчеру КС-2 о начале работ и об обнаруженном ложном срабатывании светозвукового извещателя системы газовой сигнализации (вызванном кратковременным сбоем газоанализатора CS2-29QT-1102), чем нарушили условия договора (пункт 5.4.7). При осмотре кнопка ESD-3 была обнаружена в активированном состоянии.</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Деактивация кнопки системы аварийной защиты ESD-3. Проверка логики работы системы ПАЗ (ESD) — замечаний не выявлено. Кнопка приведена в исходное состояние, произведён запуск ГПА-3.</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала КС-2 ошибок не выявлено. Активация сигнала ESD-3 произведена сотрудниками подрядной организации АО ИЦА, грубо нарушившими правила техники безопасности и условия договора.
+Деактивация кнопки системы аварийной защиты ESD-3. Проверка логики работы системы ПАЗ (ESD) — замечаний не выявлено. Кнопка приведена в исходное состояние, произведён запуск ГПА-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="95" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>№8 от 14.09.2025</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>14.09.2025</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Вынужденный нормальный</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Технологическое ограничение при переключении</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Согласно заявке на выполнение работ был произведён запуск ГПА№3 для переключения с ГПА№1. В процессе прогрева ГПА№3 обороты на ГПА№1 снижались с 4300 до 3800 об/мин, запас помпажа составил 11%. При достижении минимальной нагрузки на ГПА№1 (3120 об/мин) из-за низкого объёма транспортируемого газа произошло постепенное открытие антипомпажного клапана. ГПА№1 выведен в холостой ход и затем в нормальный останов; на ГПА№3 начали поднимать обороты для скорейшего закрытия антипомпажного клапана. В процессе закрытия клапана и подъёма оборотов замечено повышение температуры газа на выходе ГПА. При оборотах 3900 об/мин на ГПА№3 антипомпажный клапан закрыт на 80%, поступил предупредительный сигнал о достижении первого порога повышения температуры газа на выходе (75°C). Принято решение о вынужденном нормальном останове ГПА№3.</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Вынужденный нормальный останов ГПА№3 (ВНО) и перепуск ГПА№1. Запуск ГПА№1 произведён в 11:01.</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>В 15:00 произведено переключение с ГПА№1 на ГПА№3. Замечаний нет.
+Вынужденный нормальный останов ГПА№3 (ВНО) и перепуск ГПА№1. Запуск ГПА№1 произведён в 11:01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="95" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>№10 от 18.11.2025</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>18.11.2025</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>18.11.2025 в 09:40 произошёл автоматический останов ГПА№1 без стравливания контура. На панели HMI зафиксирован сигнал аварийного останова PC1-LSS33PG1I «Anti-Surge Isolation Valve Travel Fail» («Неисправность изоляционного клапана MOV-4101», потеря статуса положения крана). Автоматический останов был вызван потерей обратной связи по положению электроприводного крана MOV-4101, что привело к формированию сигнала о неисправности изоляционного клапана и срабатыванию защиты. Осмотр контактных соединений в клеммном блоке и магнитном пускателе, а также проверка панели управления MOV-4101 ошибок и ослабленных зажимов не выявили. Проверка дистанционного открытия/закрытия электроприводного крана замечаний не выявила.</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Осмотр электропривода MOV-4101 (ослабление контактных соединений, целостность составных частей привода, наличие ошибок на панели управления) — не выявлено. Проверка дистанционного открытия и закрытия электроприводного крана — замечаний не выявлено. 18.11.2025 в 11:13 осуществлён повторный пуск ГПА№1.</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>После повторного останова 19.11.2025 (по аналогичной ошибке) выполнена полная ревизия блока управления AUMATIC по частям (клеммные соединения, прозвонка всех цепей контроля и управления), осмотр платы на дефекты (некачественные пайки, повреждённые дорожки, следы горения, вздутые конденсаторы, трещины — не обнаружено, обрывов проводов нет), настройка и регулировка рабочих параметров привода, дополнительная диагностика цепей обратной связи, включая проверку сигналов положения, напряжения питания и целостности клеммных соединений в шкафу CLCP и на стороне привода, проверка протяжки клеммных зажимов, целостности кабеля и герметизации на соединительной коробке JB и в шкафу CLCP. Выполнена замена модуля цифрового ввода Allen-Bradley 1794-IB16 FLEX (тег №2NO50) в шкафу CLCP для дополнительного подтверждения исправности входных цепей и предотвращения повторения отказа.
+Осмотр электропривода MOV-4101 (ослабление контактных соединений, целостность составных частей привода, наличие ошибок на панели управления) — не выявлено. Проверка дистанционного открытия и закрытия электроприводного крана — замечаний не выявлено. 18.11.2025 в 11:13 осуществлён повторный пуск ГПА№1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="95" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>№10 от 19.11.2025</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>19.11.2025</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>19.11.2025 в 09:08 произошёл повторный автоматический останов ГПА№1 без стравливания контура по аналогичной ошибке, что и 18.11.2025. На панель HMI поступил сигнал аварийного останова PC1-LSS33PG1I «Anti-Surge Isolation Valve Travel Fail» — «Неисправность изоляционного клапана MOV-4101» (потеря статуса положения крана).</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>Выполнена полная ревизия блока управления AUMATIC по частям: проверка клеммных соединений, прозвонка всех схем цепи контроля и управления (штифтовые и гнездовые контакты цепи управления и электродвигателя, соединительная плата шины, реверсивные пускатели, блок выключателей направления ОТКРЫТИЕ/ЗАКРЫТИЕ). Осмотр платы на дефекты — не обнаружено. Настройка и регулировка рабочих параметров привода, дополнительная диагностика цепей обратной связи электропривода MOV-4101. Проверка протяжки клеммных зажимов, целостности кабеля и герметизации на соединительной коробке JB и в шкафу CLCP. Выполнена замена модуля цифрового ввода Allen-Bradley 1794-IB16 FLEX (тег №2NO50) в шкафу CLCP.</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>В действиях оперативного персонала ошибок не выявлено.
+Выполнена полная ревизия блока управления AUMATIC по частям: проверка клеммных соединений, прозвонка всех схем цепи контроля и управления (штифтовые и гнездовые контакты цепи управления и электродвигателя, соединительная плата шины, реверсивные пускатели, блок выключателей направления ОТКРЫТИЕ/ЗАКРЫТИЕ). Осмотр платы на дефекты — не обнаружено. Настройка и регулировка рабочих параметров привода, дополнительная диагностика цепей обратной связи электропривода MOV-4101. Проверка протяжки клеммных зажимов, целостности кабеля и герметизации на соединительной коробке JB и в шкафу CLCP. Выполнена замена модуля цифрового ввода Allen-Bradley 1794-IB16 FLEX (тег №2NO50) в шкафу CLCP.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -4694,7 +5880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4733,11 +5919,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A4)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>B4/30</f>
+        <f>B4/40</f>
         <v/>
       </c>
     </row>
@@ -4748,11 +5934,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A5)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>B5/30</f>
+        <f>B5/40</f>
         <v/>
       </c>
     </row>
@@ -4763,11 +5949,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A6)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>B6/30</f>
+        <f>B6/40</f>
         <v/>
       </c>
     </row>
@@ -4778,11 +5964,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A7)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>B7/30</f>
+        <f>B7/40</f>
         <v/>
       </c>
     </row>
@@ -4793,11 +5979,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A8)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>B8/30</f>
+        <f>B8/40</f>
         <v/>
       </c>
     </row>
@@ -4808,11 +5994,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A9)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>B9/30</f>
+        <f>B9/40</f>
         <v/>
       </c>
     </row>
@@ -4823,71 +6009,86 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A10)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>B10/30</f>
+        <f>B10/40</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Человеческий фактор</t>
+          <t>Технологическое ограничение при переключении</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A11)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>B11/30</f>
+        <f>B11/40</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Электросеть / переключение агрегатов</t>
+          <t>Человеческий фактор</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A12)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>B12/30</f>
+        <f>B12/40</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Электросеть / переключение агрегатов</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>B13/40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Электросеть / синхронизация агрегатов</t>
         </is>
       </c>
-      <c r="B13" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$33,A13)</f>
+      <c r="B14" s="3">
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A14)</f>
         <v/>
       </c>
-      <c r="C13" s="16">
-        <f>B13/30</f>
+      <c r="C14" s="16">
+        <f>B14/40</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>ИТОГО инцидентов</t>
         </is>
       </c>
-      <c r="B14" s="17">
-        <f>SUM(B4:B13)</f>
+      <c r="B15" s="17">
+        <f>SUM(B4:B14)</f>
         <v/>
       </c>
-      <c r="C14" s="18">
-        <f>SUM(C4:C13)</f>
+      <c r="C15" s="18">
+        <f>SUM(C4:C14)</f>
         <v/>
       </c>
     </row>
@@ -5124,7 +6325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5762,6 +6963,206 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act01_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>25.04.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act02_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>02.07.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>№3</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act03_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>12.07.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>№4</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act04_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>24.07.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>№5</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act05_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>03.08.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>№6</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act06_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>07.08.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>№7</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act07_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>08.08.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>№8</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act08_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>14.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>№10</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act10_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>18.11.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>№10</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>kc2_act10_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>19.11.2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2203,8 +2203,260 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2025</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2025-№1</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act01_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>20.03.2025</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>2025-№2</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act02_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>24.03.2025</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>2025-№3</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act03_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>01.04.2025</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2025-№4</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act04_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>09.05.2025</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>2025-№5</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act05_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>09.05.2025</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2025-№5</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act05_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>07.09.2025</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>2025-№6</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act06_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>13.11.2025</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2025-№7</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act07_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>13.11.2025</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>2025-№7</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act07_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Этот лист формируется автоматически из accidents.json при запуске build.py. Не редактируйте его вручную — правки потеряются при следующей пересборке.</t>
         </is>
@@ -2212,8 +2464,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2225,7 +2477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3599,6 +3851,237 @@
       </c>
       <c r="G43" s="7" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№3 из-за автоматического останова ГПЭС№4 (ошибка №1452 «Ошибка положения автомата защиты ГУ»)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2025</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№3 из-за автоматического останова ГПЭС№4 (ошибка №2489 «Перепад температуры выхлопных газов цилиндра №11 (А6)»)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>20.03.2025</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№2 из-за ложного сигнала «Подтверждённый пожар в Цеху №3» при тестировании детекторов пламени подрядчиком</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>24.03.2025</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>№3</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№2 по сигналам T22VSVTM_R/S open or short (разница сопротивления катушек сервоприводов VSV A/B)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>01.04.2025</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>№4</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Останов ГПА№1,2 из-за автоматического останова ГПЭС№4 (повторная ошибка №1452 «Ошибка положения автомата защиты ГУ»)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>09.05.2025</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>№5</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №2</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№2 из-за короткого замыкания сигнальной линии ZSH372 на корпус распределительной коробки ТВ22</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>07.09.2025</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>№6</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Останов ГПА№2,3 по срыву пламени из-за нестабильности регуляторов давления топливного газа БПТГ №1,2</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>13.11.2025</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>№7</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2, ГПА №3</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3646,6 +4129,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3700,15 +4190,15 @@
         <v>2018</v>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A4,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3717,15 +4207,15 @@
         <v>2019</v>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A5,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3734,15 +4224,15 @@
         <v>2020</v>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A6,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3751,15 +4241,15 @@
         <v>2021</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A7,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3768,15 +4258,15 @@
         <v>2022</v>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A8,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3785,15 +4275,15 @@
         <v>2023</v>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A9,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3802,15 +4292,15 @@
         <v>2024</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A10,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3819,15 +4309,15 @@
         <v>2025</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A11,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3836,15 +4326,15 @@
         <v>2026</v>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$59,База_данных!$A$4:$A$59,A12,База_данных!$B$4:$B$59,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -3855,15 +4345,15 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №1")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №1")</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №2")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №2")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$59,База_данных!$B$4:$B$59,"ГПА №3")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №3")</f>
         <v/>
       </c>
     </row>
@@ -3881,7 +4371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5863,6 +6353,339 @@
         <is>
           <t>В действиях оперативного персонала ошибок не выявлено.
 Выполнена полная ревизия блока управления AUMATIC по частям: проверка клеммных соединений, прозвонка всех схем цепи контроля и управления (штифтовые и гнездовые контакты цепи управления и электродвигателя, соединительная плата шины, реверсивные пускатели, блок выключателей направления ОТКРЫТИЕ/ЗАКРЫТИЕ). Осмотр платы на дефекты — не обнаружено. Настройка и регулировка рабочих параметров привода, дополнительная диагностика цепей обратной связи электропривода MOV-4101. Проверка протяжки клеммных зажимов, целостности кабеля и герметизации на соединительной коробке JB и в шкафу CLCP. Выполнена замена модуля цифрового ввода Allen-Bradley 1794-IB16 FLEX (тег №2NO50) в шкафу CLCP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="95" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>№1 от 03.02.2025</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>03.02.2025</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>На панель управления ГПЭС№4 поступил сигнал об ошибке №1452 «Ошибка положения автомата защиты ГУ», после чего произошёл автоматический останов ГПЭС№4, что привело к автоматическому останову ГПА№3.</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Проверка ошибки монтажа проводов, соединяющих выход управления замыканием автоматического выключателя на базовой плате (контакты ТВ5-1 и ТВ5-2) с автоматическим выключателем генераторной установки и обратной связью. Проверка настройки параллельного подключения на панели управления ГПЭС№4. Проверка монтажа проводов, соединяющих автоматический выключатель генераторной установки с базовой платой. Замена реле №38, подающего команду на замыкание автоматического выключателя. Проверка и затяжка контактов сигнальных линий ГПЭС№4 и вводного автомата. Проверка целостности проводника сигнальных линий. Запуск ГПЭС№4, синхронизация с ГПЭС№3, проверка рабочих характеристик. Проверка предохранителя FU-4. Смена местами переключателя режима автоматического выключателя с ГПЭС№1 на ГПЭС№4. Смена местами вводного автомата ГПЭС№4 и ГПЭС№1, попытка синхронизации с ГПЭС№3.</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>После восстановления подачи электропитания произведён запуск ГПА№1.
+Проверка ошибки монтажа проводов, соединяющих выход управления замыканием автоматического выключателя на базовой плате (контакты ТВ5-1 и ТВ5-2) с автоматическим выключателем генераторной установки и обратной связью. Проверка настройки параллельного подключения на панели управления ГПЭС№4. Проверка монтажа проводов, соединяющих автоматический выключатель генераторной установки с базовой платой. Замена реле №38, подающего команду на замыкание автоматического выключателя. Проверка и затяжка контактов сигнальных линий ГПЭС№4 и вводного автомата. Проверка целостности проводника сигнальных линий. Запуск ГПЭС№4, синхронизация с ГПЭС№3, проверка рабочих характеристик. Проверка предохранителя FU-4. Смена местами переключателя режима автоматического выключателя с ГПЭС№1 на ГПЭС№4. Смена местами вводного автомата ГПЭС№4 и ГПЭС№1, попытка синхронизации с ГПЭС№3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="95" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>№2 от 20.03.2025</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>20.03.2025</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Техническая неисправность оборудования</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>На панели управления ГПЭС№4 произошёл автоматический останов по ошибке №2489 «Перепад температуры выхлопных газов цилиндра №11 (А6)», что привело к автоматическому останову ГПА№3.</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>В ходе проверки цилиндра №11 (А6) выявлено, что зазор свечи зажигания увеличен до 0,53 мм (согласно руководству по эксплуатации ГПЭС зазор должен быть 0,28 мм). Проверены все зазоры свечей зажигания, произведена замена 10 свечей зажигания на имеющиеся б/у в хорошем состоянии (зазор не превышает 0,28 мм). Дополнительно: проверка сопротивления электродов свечей зажигания, проверка сопротивления обмотки катушки зажигания, осмотр и чистка внутренности катушки от нагара.</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>После восстановления подачи электропитания ГПА№3 выведен в резерв.
+В ходе проверки цилиндра №11 (А6) выявлено, что зазор свечи зажигания увеличен до 0,53 мм (согласно руководству по эксплуатации ГПЭС зазор должен быть 0,28 мм). Проверены все зазоры свечей зажигания, произведена замена 10 свечей зажигания на имеющиеся б/у в хорошем состоянии (зазор не превышает 0,28 мм). Дополнительно: проверка сопротивления электродов свечей зажигания, проверка сопротивления обмотки катушки зажигания, осмотр и чистка внутренности катушки от нагара.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="95" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>№3 от 24.03.2025</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>24.03.2025</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Ложное срабатывание КИП / связь</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Совместно с подрядной организацией ТОО «Zhetysu Service Partners» проводились работы по сервисному обслуживанию систем СПГС и АПТ на ГПА№3. В ходе поочередной активации и тестирования детекторов пламени, в момент перехода на этап тестирования ручных извещателей пожара произошло несанкционированное срабатывание ПАЗ, приведшее к формированию сигнала «Подтверждённый пожар в Цеху №3» уровня ESD-II, одновременно сгенерировавшего автоматический останов ГПА№1/2/3. Генерация выходного сигнала ПАЗ возникла в результате сбоя работы программного обеспечения Engineering WorkPlace ABB по причине нарушения работы процессора (открытые окна и вкладки MainFaceplate), инициировавшего системную ошибку операционной системы инженерной рабочей станции ES-1.</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Диагностика: проверена работа программы и проанализированы параметры сигналов в программном обеспечении Engineering WorkPlace. Приняты меры по устранению перегрузки, а также оптимизации работы программы для работы с большим количеством форсированных сигналов. Закрыты лишние окна и вкладки MainFaceplate. После устранения сбоя система была перезапущена, все сигналы проверены на корректность.</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>После сброса и восстановления ESDII ГПА№3 выведен в «работу» в 16:10.
+Диагностика: проверена работа программы и проанализированы параметры сигналов в программном обеспечении Engineering WorkPlace. Приняты меры по устранению перегрузки, а также оптимизации работы программы для работы с большим количеством форсированных сигналов. Закрыты лишние окна и вкладки MainFaceplate. После устранения сбоя система была перезапущена, все сигналы проверены на корректность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="95" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>№4 от 01.04.2025</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>01.04.2025</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>Согласно журналу предупреждений и аварийных сигналов (WorkstationST Alarm Viewer), отработали сигналы T22VSVTM_R open or short (R coil) и T22VSVTM_S open or short (S coil). Причина — разница показания сопротивления между катушками VSVVCOILOHM_R и VSVVCOILOHM_S сервоприводов VSV A/B.</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Проверка проводки на предмет обрыва и целостности цепей управления. Измерение сопротивления сервопривода, сравнение с номинальными значениями. Проверка AV-селектора в Hardware с мониторингом показаний в ServoHMI. Сравнение сопротивления с допустимыми пределами. Проверка перемычек (JP1/JP3/JP5) на плате управления на соответствие конфигурации ToolBoxST. Замена VSV сервопривода. Калибровка сервоприводов в режиме Calibration crank на ГПА-2. Замена платы управления GE IS200TSVCH1A в шкафу управления TCP-1.</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>После выполнения работ разница сопротивления между катушками R и S составила 10 Ом (нерабочий ГПА) и 100 Ом (режим Calibration Crank). ГПА№2 выведен в «резерв».
+Проверка проводки на предмет обрыва и целостности цепей управления. Измерение сопротивления сервопривода, сравнение с номинальными значениями. Проверка AV-селектора в Hardware с мониторингом показаний в ServoHMI. Сравнение сопротивления с допустимыми пределами. Проверка перемычек (JP1/JP3/JP5) на плате управления на соответствие конфигурации ToolBoxST. Замена VSV сервопривода. Калибровка сервоприводов в режиме Calibration crank на ГПА-2. Замена платы управления GE IS200TSVCH1A в шкафу управления TCP-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="95" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>№5 от 09.05.2025</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>09.05.2025</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №1, ГПА №2</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Отказ оборудования КИПиА</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>На панель управления ГПЭС№4 поступил сигнал об ошибке №1452 «Ошибка положения автомата защиты ГУ», после чего произошёл автоматический останов ГПЭС№4 по ошибке №611 «Горячий останов двигателя». Автоматический останов ГПЭС№4 привёл к автоматическому останову ГПА№1,2. Аналогичная ошибка уже фиксировалась ранее (см. Акт №1 от 03.02.2025).</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>Проверка ячейки отсека релейной защиты вводного автомата ГПЭС№4. Проверка и затяжка контактов сигнальных линий ГПЭС№4 и вводного автомата. Проверка целостности проводника сигнальных линий. Проверка монтажа проводов, соединяющих автоматический выключатель генераторной установки с базовой платой. Запуск ГПЭС№4, синхронизация с ГПЭС№2, проверка рабочих характеристик — отклонений, ошибок, замечаний не обнаружено, ГПЭС№4 выведен в резерв.</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>После восстановления подачи электропитания ГПА№1,2 выведен в резерв.
+Проверка ячейки отсека релейной защиты вводного автомата ГПЭС№4. Проверка и затяжка контактов сигнальных линий ГПЭС№4 и вводного автомата. Проверка целостности проводника сигнальных линий. Проверка монтажа проводов, соединяющих автоматический выключатель генераторной установки с базовой платой. Запуск ГПЭС№4, синхронизация с ГПЭС№2, проверка рабочих характеристик — отклонений, ошибок, замечаний не обнаружено, ГПЭС№4 выведен в резерв.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="95" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>№6 от 07.09.2025</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>07.09.2025</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Техническая неисправность оборудования</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>Согласно журналу предупреждений и аварийных сигналов (WorkstationST Alarm Viewer и Trender), во время работы ГПА№2 зафиксированы сигналы ZSH372 (HYDRAULIC PUMP MANUAL ISOLATION VALVE NOT OPEN ALARM) и EXTERNAL ESD, сформировавшие ESDII. Формирование сигнала аварийной остановки второго уровня (ESD II) было вызвано коротким замыканием сигнальной линии ZSH372 на корпус распределительной коробки ТВ22, установленной в кожухе газоперекачивающего агрегата (ГПА). Причиной короткого замыкания стало нарушение изоляции проводки вследствие её износа в результате длительного воздействия вибрации от кожуха ГПА, что привело к механическому повреждению оболочки проводов и контакту с заземлёнными элементами корпуса.</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>Проведена диагностика сигнальных цепей на участке от распределительной коробки ТВ22 до JB104 и далее до системы управления UCP Mark VI. Выполнен визуальный и приборный контроль состояния кабельной линии, выявлено повреждение изоляции в месте соприкосновения с металлическими элементами кожуха. Повреждённый участок проводки демонтирован, выполнен перемонтаж проводки с использованием наконечников и пинов для надёжности контактов. Выполнена ревизия креплений распределительной коробки ТВ22 и кабелей.
+Повреждено: Проводка сигнала ZSH372 в распределительной коробке ТВ22 — повреждена изоляция вследствие износа и вибрационного воздействия</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>После проведения комплексных мероприятий по выявлению и устранению причин аварийной остановки ГПА№2 восстановлен и полностью готов к дальнейшей эксплуатации.
+Проведена диагностика сигнальных цепей на участке от распределительной коробки ТВ22 до JB104 и далее до системы управления UCP Mark VI. Выполнен визуальный и приборный контроль состояния кабельной линии, выявлено повреждение изоляции в месте соприкосновения с металлическими элементами кожуха. Повреждённый участок проводки демонтирован, выполнен перемонтаж проводки с использованием наконечников и пинов для надёжности контактов. Выполнена ревизия креплений распределительной коробки ТВ22 и кабелей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="95" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>№7 от 13.11.2025</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>13.11.2025</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2, ГПА №3</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Техническая неисправность (вспомогательные системы)</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Согласно журналу событий SCADA, во время работы ГПА№2,3 в 19:12 зафиксированы сигналы низкого давления газа на топливной линии от датчиков PT080302 и PT080402, что привело к автоматическому останову ГПА№2,3. Причина — отказ регуляторов давления с понижением давления топливного газа, установленных в блоке подготовки топливного газа (БПТГ) №1,2. При повышении оборотов ГПА№2,3 до 6000 об/мин произошёл автоматический останов по срыву пламени в камере сгорания (ошибка Flame out trip SIS23.L28FDT alarm). При анализе трендов установлено резкое увеличение перепада давления на фильтре FSP080101 (с 18 кПа до 68,8 кПа), а также скачки расхода топливного газа на расходомере FIT080301, что могло привести к потере стабильности регулирования регуляторов давления на БПТГ№1,2.</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>Проведены работы по настройке регуляторов давления топливного газа в БПТГ№1,2, что позволило восстановить подачу топливного газа в ГПА№2,3. Проведена корректировка настроек регулятора и контроль за стабильностью давления на выходе.</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>ГПА№2,3 выведены в работу.
+Проведены работы по настройке регуляторов давления топливного газа в БПТГ№1,2, что позволило восстановить подачу топливного газа в ГПА№2,3. Проведена корректировка настроек регулятора и контроль за стабильностью давления на выходе.</t>
         </is>
       </c>
     </row>
@@ -5919,11 +6742,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A4)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>B4/40</f>
+        <f>B4/47</f>
         <v/>
       </c>
     </row>
@@ -5934,11 +6757,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A5)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>B5/40</f>
+        <f>B5/47</f>
         <v/>
       </c>
     </row>
@@ -5949,11 +6772,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A6)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>B6/40</f>
+        <f>B6/47</f>
         <v/>
       </c>
     </row>
@@ -5964,11 +6787,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A7)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>B7/40</f>
+        <f>B7/47</f>
         <v/>
       </c>
     </row>
@@ -5979,11 +6802,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A8)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>B8/40</f>
+        <f>B8/47</f>
         <v/>
       </c>
     </row>
@@ -5994,11 +6817,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A9)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>B9/40</f>
+        <f>B9/47</f>
         <v/>
       </c>
     </row>
@@ -6009,11 +6832,11 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A10)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>B10/40</f>
+        <f>B10/47</f>
         <v/>
       </c>
     </row>
@@ -6024,11 +6847,11 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A11)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>B11/40</f>
+        <f>B11/47</f>
         <v/>
       </c>
     </row>
@@ -6039,11 +6862,11 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A12)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>B12/40</f>
+        <f>B12/47</f>
         <v/>
       </c>
     </row>
@@ -6054,11 +6877,11 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A13)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>B13/40</f>
+        <f>B13/47</f>
         <v/>
       </c>
     </row>
@@ -6069,11 +6892,11 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$43,A14)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>B14/40</f>
+        <f>B14/47</f>
         <v/>
       </c>
     </row>
@@ -6325,7 +7148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7163,6 +7986,146 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act01_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>03.02.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act02_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>20.03.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>№3</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act03_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>24.03.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>№4</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act04_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>01.04.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>№5</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act05_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>09.05.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>№6</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act06_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>07.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>№7</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act07_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>13.11.2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/База_аварийных_остановов_ГПА.xlsx
+++ b/База_аварийных_остановов_ГПА.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2455,8 +2455,64 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>30.09.2024</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>2024-№1</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act08_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>30.11.2024</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>2024-№2</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>sks2_act09_investigation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Этот лист формируется автоматически из accidents.json при запуске build.py. Не редактируйте его вручную — правки потеряются при следующей пересборке.</t>
         </is>
@@ -2464,8 +2520,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2477,7 +2533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4082,6 +4138,72 @@
       </c>
       <c r="G50" s="7" t="n">
         <v>96</v>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№1,2,3 из-за срабатывания детекторов пламени (тление ветоши после огневых работ на ГПА№2)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>30.09.2024</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический останов ГПА№2 из-за низкого дифференциального давления в кожухе ГГ (сбой резервного вентилятора продувки 88BA-1)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>30.11.2024</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Открыть акт (PDF)</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4136,6 +4258,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4190,15 +4314,15 @@
         <v>2018</v>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A4,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A4,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4207,15 +4331,15 @@
         <v>2019</v>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A5,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A5,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4224,15 +4348,15 @@
         <v>2020</v>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A6,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A6,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4241,15 +4365,15 @@
         <v>2021</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A7,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A7,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4258,15 +4382,15 @@
         <v>2022</v>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A8,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A8,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4275,15 +4399,15 @@
         <v>2023</v>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A9,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A9,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4292,15 +4416,15 @@
         <v>2024</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A10,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A10,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4309,15 +4433,15 @@
         <v>2025</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A11,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A11,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4326,15 +4450,15 @@
         <v>2026</v>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №1")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №1")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №1")),"")</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №2")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №2")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №2")),"")</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$68,База_данных!$A$4:$A$68,A12,База_данных!$B$4:$B$68,"ГПА №3")),"")</f>
+        <f>IFERROR(IF(SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №3")=0,"",SUMIFS(База_данных!$C$4:$C$70,База_данных!$A$4:$A$70,A12,База_данных!$B$4:$B$70,"ГПА №3")),"")</f>
         <v/>
       </c>
     </row>
@@ -4345,15 +4469,15 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №1")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$70,База_данных!$B$4:$B$70,"ГПА №1")</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №2")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$70,База_данных!$B$4:$B$70,"ГПА №2")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>SUMIFS(База_данных!$C$4:$C$68,База_данных!$B$4:$B$68,"ГПА №3")</f>
+        <f>SUMIFS(База_данных!$C$4:$C$70,База_данных!$B$4:$B$70,"ГПА №3")</f>
         <v/>
       </c>
     </row>
@@ -4371,7 +4495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6686,6 +6810,103 @@
         <is>
           <t>ГПА№2,3 выведены в работу.
 Проведены работы по настройке регуляторов давления топливного газа в БПТГ№1,2, что позволило восстановить подачу топливного газа в ГПА№2,3. Проведена корректировка настроек регулятора и контроль за стабильностью давления на выходе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="95" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>№1 от 30.09.2024</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>30.09.2024</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №3</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Человеческий фактор</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Во время подготовительных огневых работ по демонтажу обслуживающей платформы для замены СГУ на ГПА№2 (срез опорных ножек угловой шлифовальной машиной) окалина попала на ветошь. После восстановления снятых на время работ форсировок по датчикам загазованности и пламени в 20:51 детекторы пламени XFU040207, XFU040208 зафиксировали тление ветоши, что сформировало сигнал ESD-II с активацией предпускового выброса CO2 компрессорного цеха №2 и автоматический останов ГПА№1,2,3 со сбросом давления из контура; закрылись станционные краны ESDV.</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>Сменный инженер по индикации на панели AUX определил активную индикацию предвыпуска CO2 и по приборам весового устройства перепроверил ложность выброса. Осмотр цеха без захода внутрь выявил задымление и тление ветоши у юго-восточной двери; сигнал пожаротушения деактивирован, очаг потушен огнетушителем ОП-10. Восстановление режима станции: выравнивание давления через кран MOPV311101 (ESDV311101), открытие проходного крана GHV311301, выравнивание давления между входным/выходным коллекторами КС через кольцо FCV010001, выравнивание давления через ESDV311201, закрытие GHV311301.</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>ГПА №3 выведен в «резерв» 30.09.2024 в 23:00.
+Сменный инженер по индикации на панели AUX определил активную индикацию предвыпуска CO2 и по приборам весового устройства перепроверил ложность выброса. Осмотр цеха без захода внутрь выявил задымление и тление ветоши у юго-восточной двери; сигнал пожаротушения деактивирован, очаг потушен огнетушителем ОП-10. Восстановление режима станции: выравнивание давления через кран MOPV311101 (ESDV311101), открытие проходного крана GHV311301, выравнивание давления между входным/выходным коллекторами КС через кольцо FCV010001, выравнивание давления через ESDV311201, закрытие GHV311301.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="95" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>№2 от 30.11.2024</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>30.11.2024</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>ГПА №2</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Автоматический</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>Техническая неисправность (вспомогательные системы)</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>После сообщения о низком давлении от датчиков РТ-130001/002/003 на выходе воздушного компрессора №1 произведено оперативное переключение на ВК№2. При переключении на резервный вентилятор продувки кожуха ГТУ (88ВА-1) зафиксирована ошибка «Сбой питания сети (А36)» частотного преобразователя; резервный вентилятор подхватил запуск только через 8 секунд, за это время дифференциальное давление внутри кожуха ГГ (датчик PDIT-270) кратковременно снизилось ниже нормы, что привело к автоматическому останову ГПА№2 без сброса давления из контура.</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>Проверка историй трендов питающей сети в HMI; проверка ошибок в контроллерах частотных преобразователей вентиляторов 88ВА-1 и 88ВА-2 в МСС№2; проверка установленных защит частотных преобразователей; дистанционный запуск вентиляторов; проверка рабочих параметров.
+Повреждено: Не обнаружено</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>ГПА №2 выведен в «резерв» 30.11.2024 в 23:00.
+Проверка историй трендов питающей сети в HMI; проверка ошибок в контроллерах частотных преобразователей вентиляторов 88ВА-1 и 88ВА-2 в МСС№2; проверка установленных защит частотных преобразователей; дистанционный запуск вентиляторов; проверка рабочих параметров.</t>
         </is>
       </c>
     </row>
@@ -6742,11 +6963,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A4)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>B4/47</f>
+        <f>B4/49</f>
         <v/>
       </c>
     </row>
@@ -6757,11 +6978,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A5)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>B5/47</f>
+        <f>B5/49</f>
         <v/>
       </c>
     </row>
@@ -6772,11 +6993,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A6)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>B6/47</f>
+        <f>B6/49</f>
         <v/>
       </c>
     </row>
@@ -6787,11 +7008,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A7)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>B7/47</f>
+        <f>B7/49</f>
         <v/>
       </c>
     </row>
@@ -6802,11 +7023,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A8)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>B8/47</f>
+        <f>B8/49</f>
         <v/>
       </c>
     </row>
@@ -6817,11 +7038,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A9)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>B9/47</f>
+        <f>B9/49</f>
         <v/>
       </c>
     </row>
@@ -6832,11 +7053,11 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A10)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>B10/47</f>
+        <f>B10/49</f>
         <v/>
       </c>
     </row>
@@ -6847,11 +7068,11 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A11)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>B11/47</f>
+        <f>B11/49</f>
         <v/>
       </c>
     </row>
@@ -6862,11 +7083,11 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A12)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>B12/47</f>
+        <f>B12/49</f>
         <v/>
       </c>
     </row>
@@ -6877,11 +7098,11 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A13)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>B13/47</f>
+        <f>B13/49</f>
         <v/>
       </c>
     </row>
@@ -6892,11 +7113,11 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>COUNTIF('Инциденты_детально'!$F$4:$F$50,A14)</f>
+        <f>COUNTIF('Инциденты_детально'!$F$4:$F$52,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>B14/47</f>
+        <f>B14/49</f>
         <v/>
       </c>
     </row>
@@ -7148,7 +7369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8126,6 +8347,46 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>№1</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act08_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>30.09.2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>№2</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>sks2_act09_investigation.pdf</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>30.11.2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
